--- a/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderSales.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderSales.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>虚拟仓</t>
   </si>
@@ -71,6 +71,15 @@
     <t>剩余需求总数</t>
   </si>
   <si>
+    <t>B2B需求数</t>
+  </si>
+  <si>
+    <t>B2C需求数</t>
+  </si>
+  <si>
+    <t>头程需求数</t>
+  </si>
+  <si>
     <t>虚拟仓可用</t>
   </si>
   <si>
@@ -129,6 +138,15 @@
   </si>
   <si>
     <t>{.totalQty}</t>
+  </si>
+  <si>
+    <t>{.b2bQty}</t>
+  </si>
+  <si>
+    <t>{.b2cQty}</t>
+  </si>
+  <si>
+    <t>{.firstMileQty}</t>
   </si>
   <si>
     <t>{.virtualUsableQty}</t>
@@ -1077,7 +1095,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
@@ -1092,15 +1110,18 @@
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="11.375" customWidth="1"/>
     <col min="14" max="14" width="14.125" customWidth="1"/>
-    <col min="15" max="15" width="12.75" customWidth="1"/>
-    <col min="16" max="16" width="12.375" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="11.125" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="15.75" customWidth="1"/>
+    <col min="15" max="15" width="14.25" customWidth="1"/>
+    <col min="16" max="16" width="13.875" customWidth="1"/>
+    <col min="17" max="17" width="13.75" customWidth="1"/>
+    <col min="18" max="18" width="12.75" customWidth="1"/>
+    <col min="19" max="19" width="12.375" customWidth="1"/>
+    <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="21" max="21" width="11.125" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
+    <col min="23" max="23" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1161,67 +1182,85 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="T2" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="U2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderSales.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderSales.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>虚拟仓</t>
   </si>
@@ -95,6 +95,12 @@
     <t>累计分配</t>
   </si>
   <si>
+    <t>近30日出库</t>
+  </si>
+  <si>
+    <t>近30日分配</t>
+  </si>
+  <si>
     <t>更新时间</t>
   </si>
   <si>
@@ -162,6 +168,12 @@
   </si>
   <si>
     <t>{.distributionQty}</t>
+  </si>
+  <si>
+    <t>{.thirtyDaysOutstockQty}</t>
+  </si>
+  <si>
+    <t>{.thirtyDaysDistributionQty}</t>
   </si>
   <si>
     <t>{.updateTime}</t>
@@ -1095,7 +1107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
@@ -1118,10 +1130,10 @@
     <col min="20" max="20" width="13" customWidth="1"/>
     <col min="21" max="21" width="11.125" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
-    <col min="23" max="23" width="15.75" customWidth="1"/>
+    <col min="23" max="25" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1191,76 +1203,88 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="T2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="U2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="W2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="X2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderSales.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderSales.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>虚拟仓</t>
   </si>
@@ -80,6 +80,9 @@
     <t>头程需求数</t>
   </si>
   <si>
+    <t>实体仓分配</t>
+  </si>
+  <si>
     <t>虚拟仓可用</t>
   </si>
   <si>
@@ -153,6 +156,9 @@
   </si>
   <si>
     <t>{.firstMileQty}</t>
+  </si>
+  <si>
+    <t>{.unDistributionQty}</t>
   </si>
   <si>
     <t>{.virtualUsableQty}</t>
@@ -1107,7 +1113,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
@@ -1124,16 +1130,16 @@
     <col min="14" max="14" width="14.125" customWidth="1"/>
     <col min="15" max="15" width="14.25" customWidth="1"/>
     <col min="16" max="16" width="13.875" customWidth="1"/>
-    <col min="17" max="17" width="13.75" customWidth="1"/>
-    <col min="18" max="18" width="12.75" customWidth="1"/>
-    <col min="19" max="19" width="12.375" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
-    <col min="21" max="21" width="11.125" customWidth="1"/>
-    <col min="22" max="22" width="14" customWidth="1"/>
-    <col min="23" max="25" width="15.75" customWidth="1"/>
+    <col min="17" max="17" width="15.5" customWidth="1"/>
+    <col min="18" max="19" width="16" customWidth="1"/>
+    <col min="20" max="20" width="16.125" customWidth="1"/>
+    <col min="21" max="21" width="14.125" customWidth="1"/>
+    <col min="22" max="22" width="12.75" customWidth="1"/>
+    <col min="23" max="23" width="14.625" customWidth="1"/>
+    <col min="24" max="26" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1209,82 +1215,88 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y2" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderSales.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/reportOrderSales.xlsx
@@ -80,7 +80,7 @@
     <t>头程需求数</t>
   </si>
   <si>
-    <t>实体仓分配</t>
+    <t>实体仓未分配</t>
   </si>
   <si>
     <t>虚拟仓可用</t>
